--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125931398</v>
+        <v>125932186</v>
       </c>
       <c r="B7" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488879</v>
+        <v>488858</v>
       </c>
       <c r="R7" t="n">
-        <v>6819474</v>
+        <v>6819406</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125932186</v>
+        <v>125931398</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488858</v>
+        <v>488879</v>
       </c>
       <c r="R8" t="n">
-        <v>6819406</v>
+        <v>6819474</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1328,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125931240</v>
+        <v>125931618</v>
       </c>
       <c r="B2" t="n">
-        <v>80070</v>
+        <v>79586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488704</v>
+        <v>488844</v>
       </c>
       <c r="R2" t="n">
-        <v>6819434</v>
+        <v>6819433</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931618</v>
+        <v>125931240</v>
       </c>
       <c r="B3" t="n">
-        <v>79585</v>
+        <v>80071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488844</v>
+        <v>488704</v>
       </c>
       <c r="R3" t="n">
-        <v>6819433</v>
+        <v>6819434</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>125932005</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125931552</v>
       </c>
       <c r="B5" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125931734</v>
       </c>
       <c r="B6" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125932186</v>
+        <v>125931398</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>80100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488858</v>
+        <v>488879</v>
       </c>
       <c r="R7" t="n">
-        <v>6819406</v>
+        <v>6819474</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,48 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125931398</v>
+        <v>125932186</v>
       </c>
       <c r="B8" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488879</v>
+        <v>488858</v>
       </c>
       <c r="R8" t="n">
-        <v>6819474</v>
+        <v>6819406</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1333,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125932706</v>
+        <v>125931952</v>
       </c>
       <c r="B9" t="n">
-        <v>80105</v>
+        <v>78726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488863</v>
+        <v>488792</v>
       </c>
       <c r="R9" t="n">
-        <v>6819167</v>
+        <v>6819271</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125931952</v>
+        <v>125932706</v>
       </c>
       <c r="B10" t="n">
-        <v>78725</v>
+        <v>80106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488792</v>
+        <v>488863</v>
       </c>
       <c r="R10" t="n">
-        <v>6819271</v>
+        <v>6819167</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932588</v>
+        <v>125932508</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R11" t="n">
-        <v>6819129</v>
+        <v>6819168</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932508</v>
+        <v>125932588</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R12" t="n">
-        <v>6819168</v>
+        <v>6819129</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B13" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R13" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R14" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
         <v>125932334</v>
       </c>
       <c r="B15" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125931360</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>125931429</v>
       </c>
       <c r="B19" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>125932626</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125931570</v>
       </c>
       <c r="B21" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125932341</v>
+        <v>125931286</v>
       </c>
       <c r="B22" t="n">
-        <v>78725</v>
+        <v>80071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488872</v>
+        <v>488727</v>
       </c>
       <c r="R22" t="n">
-        <v>6819259</v>
+        <v>6819441</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125931286</v>
+        <v>125932341</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>78726</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488727</v>
+        <v>488872</v>
       </c>
       <c r="R23" t="n">
-        <v>6819441</v>
+        <v>6819259</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125931618</v>
+        <v>125932005</v>
       </c>
       <c r="B2" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488844</v>
+        <v>488787</v>
       </c>
       <c r="R2" t="n">
-        <v>6819433</v>
+        <v>6819273</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931240</v>
+        <v>125931618</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>79586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488704</v>
+        <v>488844</v>
       </c>
       <c r="R3" t="n">
-        <v>6819434</v>
+        <v>6819433</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125932005</v>
+        <v>125931240</v>
       </c>
       <c r="B4" t="n">
-        <v>78727</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488787</v>
+        <v>488704</v>
       </c>
       <c r="R4" t="n">
-        <v>6819273</v>
+        <v>6819434</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932508</v>
+        <v>125932588</v>
       </c>
       <c r="B11" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R11" t="n">
-        <v>6819168</v>
+        <v>6819129</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932588</v>
+        <v>125932508</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R12" t="n">
-        <v>6819129</v>
+        <v>6819168</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R13" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R14" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932588</v>
+        <v>125932508</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R11" t="n">
-        <v>6819129</v>
+        <v>6819168</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932508</v>
+        <v>125932588</v>
       </c>
       <c r="B12" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R12" t="n">
-        <v>6819168</v>
+        <v>6819129</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125932463</v>
+        <v>125931429</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488857</v>
+        <v>488866</v>
       </c>
       <c r="R18" t="n">
-        <v>6819190</v>
+        <v>6819473</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2322,22 +2317,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125931429</v>
+        <v>125932463</v>
       </c>
       <c r="B19" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2340,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488866</v>
+        <v>488857</v>
       </c>
       <c r="R19" t="n">
-        <v>6819473</v>
+        <v>6819190</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125932005</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125931618</v>
       </c>
       <c r="B3" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125931240</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125931552</v>
       </c>
       <c r="B5" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125931734</v>
       </c>
       <c r="B6" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125931398</v>
       </c>
       <c r="B7" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125931952</v>
       </c>
       <c r="B9" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125932706</v>
       </c>
       <c r="B10" t="n">
-        <v>80106</v>
+        <v>80110</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932508</v>
+        <v>125932588</v>
       </c>
       <c r="B11" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R11" t="n">
-        <v>6819168</v>
+        <v>6819129</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932588</v>
+        <v>125932508</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R12" t="n">
-        <v>6819129</v>
+        <v>6819168</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B13" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R13" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R14" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
         <v>125932334</v>
       </c>
       <c r="B15" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125931360</v>
       </c>
       <c r="B17" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125931429</v>
+        <v>125932463</v>
       </c>
       <c r="B18" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488866</v>
+        <v>488857</v>
       </c>
       <c r="R18" t="n">
-        <v>6819473</v>
+        <v>6819190</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2317,22 +2322,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125932463</v>
+        <v>125931429</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488857</v>
+        <v>488866</v>
       </c>
       <c r="R19" t="n">
-        <v>6819190</v>
+        <v>6819473</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2400,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
         <v>125932626</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125931570</v>
       </c>
       <c r="B21" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125931286</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125932341</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125932005</v>
+        <v>125931618</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488787</v>
+        <v>488844</v>
       </c>
       <c r="R2" t="n">
-        <v>6819273</v>
+        <v>6819433</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931618</v>
+        <v>125931240</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488844</v>
+        <v>488704</v>
       </c>
       <c r="R3" t="n">
-        <v>6819433</v>
+        <v>6819434</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125931240</v>
+        <v>125932005</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488704</v>
+        <v>488787</v>
       </c>
       <c r="R4" t="n">
-        <v>6819434</v>
+        <v>6819273</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125932463</v>
+        <v>125931429</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488857</v>
+        <v>488866</v>
       </c>
       <c r="R18" t="n">
-        <v>6819190</v>
+        <v>6819473</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2322,22 +2317,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125931429</v>
+        <v>125932463</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2340,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488866</v>
+        <v>488857</v>
       </c>
       <c r="R19" t="n">
-        <v>6819473</v>
+        <v>6819190</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125931618</v>
       </c>
       <c r="B2" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125931240</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125932005</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125931552</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125931734</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125931398</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125932186</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125931952</v>
       </c>
       <c r="B9" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125932706</v>
       </c>
       <c r="B10" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125932588</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125932508</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125931252</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>125932004</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125932334</v>
       </c>
       <c r="B15" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125931360</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125931429</v>
       </c>
       <c r="B18" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125932463</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>125932626</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125931570</v>
       </c>
       <c r="B21" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125931286</v>
+        <v>125932341</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488727</v>
+        <v>488872</v>
       </c>
       <c r="R22" t="n">
-        <v>6819441</v>
+        <v>6819259</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125932341</v>
+        <v>125931286</v>
       </c>
       <c r="B23" t="n">
-        <v>78730</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488872</v>
+        <v>488727</v>
       </c>
       <c r="R23" t="n">
-        <v>6819259</v>
+        <v>6819441</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R13" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R14" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125932341</v>
+        <v>125931286</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488872</v>
+        <v>488727</v>
       </c>
       <c r="R22" t="n">
-        <v>6819259</v>
+        <v>6819441</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125931286</v>
+        <v>125932341</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488727</v>
+        <v>488872</v>
       </c>
       <c r="R23" t="n">
-        <v>6819441</v>
+        <v>6819259</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R13" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R14" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125931286</v>
+        <v>125932341</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488727</v>
+        <v>488872</v>
       </c>
       <c r="R22" t="n">
-        <v>6819441</v>
+        <v>6819259</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125932341</v>
+        <v>125931286</v>
       </c>
       <c r="B23" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488872</v>
+        <v>488727</v>
       </c>
       <c r="R23" t="n">
-        <v>6819259</v>
+        <v>6819441</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125931618</v>
+        <v>125932005</v>
       </c>
       <c r="B2" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488844</v>
+        <v>488787</v>
       </c>
       <c r="R2" t="n">
-        <v>6819433</v>
+        <v>6819273</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931240</v>
+        <v>125931618</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>79591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488704</v>
+        <v>488844</v>
       </c>
       <c r="R3" t="n">
-        <v>6819434</v>
+        <v>6819433</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125932005</v>
+        <v>125931240</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488787</v>
+        <v>488704</v>
       </c>
       <c r="R4" t="n">
-        <v>6819273</v>
+        <v>6819434</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125931398</v>
+        <v>125932186</v>
       </c>
       <c r="B7" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488879</v>
+        <v>488858</v>
       </c>
       <c r="R7" t="n">
-        <v>6819474</v>
+        <v>6819406</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125932186</v>
+        <v>125931398</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>80105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488858</v>
+        <v>488879</v>
       </c>
       <c r="R8" t="n">
-        <v>6819406</v>
+        <v>6819474</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1328,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932588</v>
+        <v>125932508</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R11" t="n">
-        <v>6819129</v>
+        <v>6819168</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932508</v>
+        <v>125932588</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R12" t="n">
-        <v>6819168</v>
+        <v>6819129</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125932005</v>
+        <v>125931618</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488787</v>
+        <v>488844</v>
       </c>
       <c r="R2" t="n">
-        <v>6819273</v>
+        <v>6819433</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931618</v>
+        <v>125931240</v>
       </c>
       <c r="B3" t="n">
-        <v>79591</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488844</v>
+        <v>488704</v>
       </c>
       <c r="R3" t="n">
-        <v>6819433</v>
+        <v>6819434</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125931240</v>
+        <v>125932005</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488704</v>
+        <v>488787</v>
       </c>
       <c r="R4" t="n">
-        <v>6819434</v>
+        <v>6819273</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>125931552</v>
       </c>
       <c r="B5" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125931734</v>
       </c>
       <c r="B6" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125932186</v>
+        <v>125931398</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>80109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488858</v>
+        <v>488879</v>
       </c>
       <c r="R7" t="n">
-        <v>6819406</v>
+        <v>6819474</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,48 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125931398</v>
+        <v>125932186</v>
       </c>
       <c r="B8" t="n">
-        <v>80105</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488879</v>
+        <v>488858</v>
       </c>
       <c r="R8" t="n">
-        <v>6819474</v>
+        <v>6819406</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1333,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,7 +1362,7 @@
         <v>125931952</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125932706</v>
       </c>
       <c r="B10" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932508</v>
+        <v>125932588</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R11" t="n">
-        <v>6819168</v>
+        <v>6819129</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932588</v>
+        <v>125932508</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R12" t="n">
-        <v>6819129</v>
+        <v>6819168</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R13" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R14" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
         <v>125932334</v>
       </c>
       <c r="B15" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125931360</v>
       </c>
       <c r="B17" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125931429</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125932463</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>125932626</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125931570</v>
       </c>
       <c r="B21" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125932341</v>
+        <v>125931286</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488872</v>
+        <v>488727</v>
       </c>
       <c r="R22" t="n">
-        <v>6819259</v>
+        <v>6819441</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125931286</v>
+        <v>125932341</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>78735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488727</v>
+        <v>488872</v>
       </c>
       <c r="R23" t="n">
-        <v>6819441</v>
+        <v>6819259</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R13" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R14" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125931618</v>
+        <v>125932005</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488844</v>
+        <v>488787</v>
       </c>
       <c r="R2" t="n">
-        <v>6819433</v>
+        <v>6819273</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931240</v>
+        <v>125931618</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488704</v>
+        <v>488844</v>
       </c>
       <c r="R3" t="n">
-        <v>6819434</v>
+        <v>6819433</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125932005</v>
+        <v>125931240</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488787</v>
+        <v>488704</v>
       </c>
       <c r="R4" t="n">
-        <v>6819273</v>
+        <v>6819434</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125931952</v>
+        <v>125932706</v>
       </c>
       <c r="B9" t="n">
-        <v>78735</v>
+        <v>80115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488792</v>
+        <v>488863</v>
       </c>
       <c r="R9" t="n">
-        <v>6819271</v>
+        <v>6819167</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125932706</v>
+        <v>125931952</v>
       </c>
       <c r="B10" t="n">
-        <v>80115</v>
+        <v>78735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488863</v>
+        <v>488792</v>
       </c>
       <c r="R10" t="n">
-        <v>6819167</v>
+        <v>6819271</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125932005</v>
+        <v>125931240</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488787</v>
+        <v>488704</v>
       </c>
       <c r="R2" t="n">
-        <v>6819273</v>
+        <v>6819434</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125931240</v>
+        <v>125932005</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488704</v>
+        <v>488787</v>
       </c>
       <c r="R4" t="n">
-        <v>6819434</v>
+        <v>6819273</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125931429</v>
+        <v>125932463</v>
       </c>
       <c r="B18" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488866</v>
+        <v>488857</v>
       </c>
       <c r="R18" t="n">
-        <v>6819473</v>
+        <v>6819190</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2317,22 +2322,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125932463</v>
+        <v>125931429</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>78735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488857</v>
+        <v>488866</v>
       </c>
       <c r="R19" t="n">
-        <v>6819190</v>
+        <v>6819473</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2400,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125931286</v>
+        <v>125932341</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>78735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488727</v>
+        <v>488872</v>
       </c>
       <c r="R22" t="n">
-        <v>6819441</v>
+        <v>6819259</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125932341</v>
+        <v>125931286</v>
       </c>
       <c r="B23" t="n">
-        <v>78735</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488872</v>
+        <v>488727</v>
       </c>
       <c r="R23" t="n">
-        <v>6819259</v>
+        <v>6819441</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125932463</v>
+        <v>125931429</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>78735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488857</v>
+        <v>488866</v>
       </c>
       <c r="R18" t="n">
-        <v>6819190</v>
+        <v>6819473</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2322,22 +2317,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125931429</v>
+        <v>125932463</v>
       </c>
       <c r="B19" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2340,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488866</v>
+        <v>488857</v>
       </c>
       <c r="R19" t="n">
-        <v>6819473</v>
+        <v>6819190</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125931240</v>
+        <v>125932005</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488704</v>
+        <v>488787</v>
       </c>
       <c r="R2" t="n">
-        <v>6819434</v>
+        <v>6819273</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931618</v>
+        <v>125931240</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488844</v>
+        <v>488704</v>
       </c>
       <c r="R3" t="n">
-        <v>6819433</v>
+        <v>6819434</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125932005</v>
+        <v>125931618</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>79598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488787</v>
+        <v>488844</v>
       </c>
       <c r="R4" t="n">
-        <v>6819273</v>
+        <v>6819433</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>125931552</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125931734</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125931398</v>
       </c>
       <c r="B7" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125932186</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125932706</v>
       </c>
       <c r="B9" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125931952</v>
       </c>
       <c r="B10" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125932588</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125932508</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R13" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B14" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R14" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
         <v>125932334</v>
       </c>
       <c r="B15" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125932580</v>
       </c>
       <c r="B16" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125931360</v>
       </c>
       <c r="B17" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125931429</v>
+        <v>125932463</v>
       </c>
       <c r="B18" t="n">
-        <v>78735</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488866</v>
+        <v>488857</v>
       </c>
       <c r="R18" t="n">
-        <v>6819473</v>
+        <v>6819190</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2317,22 +2322,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125932463</v>
+        <v>125931429</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>78738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488857</v>
+        <v>488866</v>
       </c>
       <c r="R19" t="n">
-        <v>6819190</v>
+        <v>6819473</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2400,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
         <v>125932626</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125931570</v>
       </c>
       <c r="B21" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125932341</v>
       </c>
       <c r="B22" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125931286</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932588</v>
+        <v>125932508</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R11" t="n">
-        <v>6819129</v>
+        <v>6819168</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1638,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932508</v>
+        <v>125932588</v>
       </c>
       <c r="B12" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R12" t="n">
-        <v>6819168</v>
+        <v>6819129</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125932341</v>
+        <v>125931286</v>
       </c>
       <c r="B22" t="n">
-        <v>78738</v>
+        <v>80083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488872</v>
+        <v>488727</v>
       </c>
       <c r="R22" t="n">
-        <v>6819259</v>
+        <v>6819441</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125931286</v>
+        <v>125932341</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>78738</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488727</v>
+        <v>488872</v>
       </c>
       <c r="R23" t="n">
-        <v>6819441</v>
+        <v>6819259</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125932005</v>
+        <v>125931618</v>
       </c>
       <c r="B2" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488787</v>
+        <v>488844</v>
       </c>
       <c r="R2" t="n">
-        <v>6819273</v>
+        <v>6819433</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125931618</v>
+        <v>125932005</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488844</v>
+        <v>488787</v>
       </c>
       <c r="R4" t="n">
-        <v>6819433</v>
+        <v>6819273</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125931398</v>
+        <v>125932186</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488879</v>
+        <v>488858</v>
       </c>
       <c r="R7" t="n">
-        <v>6819474</v>
+        <v>6819406</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125932186</v>
+        <v>125931398</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>80112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488858</v>
+        <v>488879</v>
       </c>
       <c r="R8" t="n">
-        <v>6819406</v>
+        <v>6819474</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1328,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125932004</v>
+        <v>125931252</v>
       </c>
       <c r="B13" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R13" t="n">
-        <v>6819300</v>
+        <v>6819491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125931252</v>
+        <v>125932004</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,34 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488977</v>
+        <v>488870</v>
       </c>
       <c r="R14" t="n">
-        <v>6819491</v>
+        <v>6819300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125932463</v>
+        <v>125931429</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>78738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488857</v>
+        <v>488866</v>
       </c>
       <c r="R18" t="n">
-        <v>6819190</v>
+        <v>6819473</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2322,22 +2317,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125931429</v>
+        <v>125932463</v>
       </c>
       <c r="B19" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2340,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488866</v>
+        <v>488857</v>
       </c>
       <c r="R19" t="n">
-        <v>6819473</v>
+        <v>6819190</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125932186</v>
+        <v>125931398</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488858</v>
+        <v>488879</v>
       </c>
       <c r="R7" t="n">
-        <v>6819406</v>
+        <v>6819474</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,48 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125931398</v>
+        <v>125932186</v>
       </c>
       <c r="B8" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488879</v>
+        <v>488858</v>
       </c>
       <c r="R8" t="n">
-        <v>6819474</v>
+        <v>6819406</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1333,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125932706</v>
+        <v>125931952</v>
       </c>
       <c r="B9" t="n">
-        <v>80118</v>
+        <v>78738</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488863</v>
+        <v>488792</v>
       </c>
       <c r="R9" t="n">
-        <v>6819167</v>
+        <v>6819271</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125931952</v>
+        <v>125932706</v>
       </c>
       <c r="B10" t="n">
-        <v>78738</v>
+        <v>80118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488792</v>
+        <v>488863</v>
       </c>
       <c r="R10" t="n">
-        <v>6819271</v>
+        <v>6819167</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125931398</v>
+        <v>125932186</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488879</v>
+        <v>488858</v>
       </c>
       <c r="R7" t="n">
-        <v>6819474</v>
+        <v>6819406</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125932186</v>
+        <v>125931398</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>80112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488858</v>
+        <v>488879</v>
       </c>
       <c r="R8" t="n">
-        <v>6819406</v>
+        <v>6819474</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1328,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125931952</v>
+        <v>125932706</v>
       </c>
       <c r="B9" t="n">
-        <v>78738</v>
+        <v>80118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488792</v>
+        <v>488863</v>
       </c>
       <c r="R9" t="n">
-        <v>6819271</v>
+        <v>6819167</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125932706</v>
+        <v>125931952</v>
       </c>
       <c r="B10" t="n">
-        <v>80118</v>
+        <v>78738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488863</v>
+        <v>488792</v>
       </c>
       <c r="R10" t="n">
-        <v>6819167</v>
+        <v>6819271</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2817,6 +2817,314 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129424043</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91469</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Griseoporia carbonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Herostjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>488798</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6819274</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer tillsammans med vad jag gissar är trollskinn, Thujacorticium zurhausenii.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129424026</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90572</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Herostjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>488863</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6819428</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129424071</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90572</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Herostjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>488798</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6819274</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2819,32 +2819,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129424043</v>
+        <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>91469</v>
+        <v>90575</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2013</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488798</v>
+        <v>488863</v>
       </c>
       <c r="R24" t="n">
-        <v>6819274</v>
+        <v>6819428</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2893,11 +2893,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Växer tillsammans med vad jag gissar är trollskinn, Thujacorticium zurhausenii.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2925,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129424026</v>
+        <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488863</v>
+        <v>488798</v>
       </c>
       <c r="R25" t="n">
-        <v>6819428</v>
+        <v>6819274</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,107 +3018,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>129424071</v>
-      </c>
-      <c r="B26" t="n">
-        <v>90572</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Anomoporia kamtschatica</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Herostjärn, Dlr</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>488798</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6819274</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Los</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-10-29</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90585</v>
+        <v>90613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90585</v>
+        <v>90613</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -2822,7 +2822,7 @@
         <v>129424026</v>
       </c>
       <c r="B24" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>129424071</v>
       </c>
       <c r="B25" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125931618</v>
+        <v>125931570</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488844</v>
+        <v>488858</v>
       </c>
       <c r="R2" t="n">
-        <v>6819433</v>
+        <v>6819434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125931240</v>
+        <v>129424026</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Herostjärn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488704</v>
+        <v>488863</v>
       </c>
       <c r="R3" t="n">
-        <v>6819434</v>
+        <v>6819428</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -851,28 +854,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125932005</v>
+        <v>129424071</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +884,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Herostjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488787</v>
+        <v>488798</v>
       </c>
       <c r="R4" t="n">
-        <v>6819273</v>
+        <v>6819274</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -948,28 +955,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125931552</v>
+        <v>125932580</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1009,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488869</v>
+        <v>488853</v>
       </c>
       <c r="R5" t="n">
-        <v>6819436</v>
+        <v>6819129</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,45 +1071,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125931734</v>
+        <v>125931252</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488870</v>
+        <v>488977</v>
       </c>
       <c r="R6" t="n">
-        <v>6819420</v>
+        <v>6819491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,48 +1168,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125931398</v>
+        <v>125932588</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488879</v>
+        <v>488853</v>
       </c>
       <c r="R7" t="n">
-        <v>6819474</v>
+        <v>6819129</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,32 +1265,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125932186</v>
+        <v>125932626</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1295,10 +1303,10 @@
         <v>488858</v>
       </c>
       <c r="R8" t="n">
-        <v>6819406</v>
+        <v>6819146</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1328,11 +1336,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125931952</v>
+        <v>125931429</v>
       </c>
       <c r="B9" t="n">
-        <v>78738</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,14 +1393,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488792</v>
+        <v>488866</v>
       </c>
       <c r="R9" t="n">
-        <v>6819271</v>
+        <v>6819473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,44 +1447,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125932706</v>
+        <v>125931952</v>
       </c>
       <c r="B10" t="n">
-        <v>80118</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,13 +1494,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488863</v>
+        <v>488792</v>
       </c>
       <c r="R10" t="n">
-        <v>6819167</v>
+        <v>6819271</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125932508</v>
+        <v>125932341</v>
       </c>
       <c r="B11" t="n">
-        <v>78739</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488869</v>
+        <v>488872</v>
       </c>
       <c r="R11" t="n">
-        <v>6819168</v>
+        <v>6819259</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125932588</v>
+        <v>125931552</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,13 +1688,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488853</v>
+        <v>488869</v>
       </c>
       <c r="R12" t="n">
-        <v>6819129</v>
+        <v>6819436</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1747,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125931252</v>
+        <v>125931618</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1761,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488977</v>
+        <v>488844</v>
       </c>
       <c r="R13" t="n">
-        <v>6819491</v>
+        <v>6819433</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125932004</v>
+        <v>125931734</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,7 +1885,7 @@
         <v>488870</v>
       </c>
       <c r="R14" t="n">
-        <v>6819300</v>
+        <v>6819420</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125932334</v>
+        <v>125931240</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1955,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,13 +1979,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488917</v>
+        <v>488704</v>
       </c>
       <c r="R15" t="n">
-        <v>6819271</v>
+        <v>6819434</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2026,44 +2029,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125932580</v>
+        <v>125931286</v>
       </c>
       <c r="B16" t="n">
-        <v>92535</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,13 +2076,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488853</v>
+        <v>488727</v>
       </c>
       <c r="R16" t="n">
-        <v>6819129</v>
+        <v>6819441</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2123,60 +2126,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125931360</v>
+        <v>125931398</v>
       </c>
       <c r="B17" t="n">
-        <v>78739</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Heros, Heros, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488745</v>
+        <v>488879</v>
       </c>
       <c r="R17" t="n">
-        <v>6819466</v>
+        <v>6819474</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2220,60 +2223,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125931429</v>
+        <v>125932706</v>
       </c>
       <c r="B18" t="n">
-        <v>78738</v>
+        <v>80467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Heros, Heros, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488866</v>
+        <v>488863</v>
       </c>
       <c r="R18" t="n">
-        <v>6819473</v>
+        <v>6819167</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2317,22 +2320,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125932463</v>
+        <v>125932186</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,13 +2367,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488857</v>
+        <v>488858</v>
       </c>
       <c r="R19" t="n">
-        <v>6819190</v>
+        <v>6819406</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2404,7 +2407,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,22 +2422,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125932626</v>
+        <v>125932463</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,13 +2469,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488858</v>
+        <v>488857</v>
       </c>
       <c r="R20" t="n">
-        <v>6819146</v>
+        <v>6819190</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2502,6 +2505,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2516,60 +2524,75 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125931570</v>
+        <v>76239860</v>
       </c>
       <c r="B21" t="n">
-        <v>78647</v>
+        <v>57144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>102613</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Orsa, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488858</v>
+        <v>488863</v>
       </c>
       <c r="R21" t="n">
-        <v>6819434</v>
+        <v>6819529</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2593,12 +2616,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2613,22 +2646,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Johan Frölinghaus</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Johan Frölinghaus</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125931286</v>
+        <v>125931360</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2636,21 +2669,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2693,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488727</v>
+        <v>488745</v>
       </c>
       <c r="R22" t="n">
-        <v>6819441</v>
+        <v>6819466</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2722,10 +2755,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125932341</v>
+        <v>125932004</v>
       </c>
       <c r="B23" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2766,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,13 +2790,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488872</v>
+        <v>488870</v>
       </c>
       <c r="R23" t="n">
-        <v>6819259</v>
+        <v>6819300</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2840,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129424026</v>
+        <v>125932005</v>
       </c>
       <c r="B24" t="n">
-        <v>90631</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,40 +2863,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Herostjärn, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488863</v>
+        <v>488787</v>
       </c>
       <c r="R24" t="n">
-        <v>6819428</v>
+        <v>6819273</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2887,12 +2917,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2901,29 +2931,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129424071</v>
+        <v>125932334</v>
       </c>
       <c r="B25" t="n">
-        <v>90631</v>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,37 +2960,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Herostjärn, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488798</v>
+        <v>488917</v>
       </c>
       <c r="R25" t="n">
-        <v>6819274</v>
+        <v>6819271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2988,12 +3014,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3002,22 +3028,118 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125932508</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>488869</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6819168</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26649-2025 artfynd.xlsx
+++ b/artfynd/A 26649-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931570</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129424026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129424071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932580</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931252</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932588</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932626</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931429</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931952</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932341</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931552</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931618</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931734</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931240</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931286</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931398</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932706</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2431,6 +2521,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932186</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932463</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2655,6 +2755,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76239860</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2752,6 +2857,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125931360</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2849,6 +2959,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932004</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2946,6 +3061,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932005</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3043,6 +3163,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932334</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3140,8 +3265,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>